--- a/output/pdf_financials_xlsx/JDN.xlsx
+++ b/output/pdf_financials_xlsx/JDN.xlsx
@@ -5954,37 +5954,37 @@
         <v>1.391851</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>-38.184881</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>-53.65576</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>-56.948829</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.993694</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.160336</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.225728</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.37838</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.359449</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>7.688044</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.173333</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>2.315132</v>
       </c>
       <c r="O92" s="3" t="n">
         <v>2.315132</v>
@@ -5993,10 +5993,10 @@
         <v>2.315132</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>2.315132</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>2.315132</v>
       </c>
     </row>
     <row r="93">
@@ -9792,7 +9792,11 @@
           <t>Reserves 2,315,132</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -11191,7 +11195,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -17078,7 +17086,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -17571,7 +17583,11 @@
           <t>Reserves 23</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -18367,7 +18383,11 @@
           <t>Reserves 22</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/JDN.xlsx
+++ b/output/pdf_financials_xlsx/JDN.xlsx
@@ -1068,37 +1068,37 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.007098</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.0009210000000000001</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.000732</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.00053</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.006358</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.000192</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.000212</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.008581999999999999</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.001894</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.008725</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>0</v>
@@ -2042,37 +2042,37 @@
         <v>-1.876804</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.069062</v>
+        <v>-2.07616</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.710083</v>
+        <v>-0.711004</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-16.57617</v>
+        <v>-16.576902</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.345427</v>
+        <v>-0.345957</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.137732</v>
+        <v>-1.14409</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>12.990798</v>
+        <v>12.990606</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>1.678283</v>
+        <v>1.678071</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-0.353064</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.656718</v>
+        <v>-0.6653</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-1.163335</v>
+        <v>-1.165229</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.600356</v>
+        <v>-0.609081</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>-0.558094</v>
@@ -2158,37 +2158,37 @@
         <v>-1.870971</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.065082</v>
+        <v>-2.07218</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.706851</v>
+        <v>-0.707772</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-16.573316</v>
+        <v>-16.574048</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.340181</v>
+        <v>-0.340711</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.136014</v>
+        <v>-1.142372</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>12.990798</v>
+        <v>12.990606</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>1.678283</v>
+        <v>1.678071</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-0.353064</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.656718</v>
+        <v>-0.6653</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-1.163335</v>
+        <v>-1.165229</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.600356</v>
+        <v>-0.609081</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>-0.558094</v>
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.395763</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>2.395763</v>
@@ -2566,7 +2566,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.038249</v>
+        <v>2.434012</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>2.433385</v>
@@ -3262,7 +3262,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.420189</v>
+        <v>0.024426</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.079371</v>
@@ -21732,7 +21732,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E133" s="5" t="n">
@@ -22245,7 +22245,11 @@
           <t>Reclamation deposits (Note 6)</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E138" s="5" t="n">
         <v>0.055</v>
       </c>
@@ -39520,7 +39524,11 @@
           <t>Write-down of environmental reclamation deposits 9</t>
         </is>
       </c>
-      <c r="D311" t="inlineStr"/>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E311" t="inlineStr">
         <is>
           <t>-</t>
@@ -41946,7 +41954,11 @@
           <t>Write-off of reclamation deposits</t>
         </is>
       </c>
-      <c r="D335" t="inlineStr"/>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E335" t="inlineStr">
         <is>
           <t>-</t>
@@ -42560,7 +42572,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E341" s="5" t="n">
         <v>-0.015</v>
       </c>
@@ -44079,7 +44095,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -44934,7 +44950,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -46449,7 +46465,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
@@ -47978,7 +47994,7 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">

--- a/output/pdf_financials_xlsx/JDN.xlsx
+++ b/output/pdf_financials_xlsx/JDN.xlsx
@@ -7062,7 +7062,7 @@
         <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.031931</v>
       </c>
       <c r="D112" s="3" t="n">
         <v>0</v>
@@ -40635,7 +40635,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr"/>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E322" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/JDN.xlsx
+++ b/output/pdf_financials_xlsx/JDN.xlsx
@@ -1312,7 +1312,7 @@
         <v>-0.345427</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>-1.137732</v>
+        <v>-0.277054</v>
       </c>
       <c r="L16" s="3" t="n">
         <v>12.990798</v>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.65</v>
+        <v>-0.65</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0.161374</v>
+        <v>-0.125</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
@@ -1370,7 +1370,7 @@
         <v>-0</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.8606780000000001</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>-0.8606780000000001</v>
@@ -1618,7 +1618,7 @@
         <v>-0.345427</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>-1.137732</v>
+        <v>-0.209203</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>-0.156617</v>
@@ -1633,10 +1633,10 @@
         <v>-0.656718</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>-1.163335</v>
+        <v>-0.619335</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>-0.600356</v>
+        <v>-0.542987</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>-0.558094</v>
@@ -1676,10 +1676,10 @@
         <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0</v>
+        <v>-0.928529</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0</v>
+        <v>-0.201485</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>0</v>
@@ -2054,7 +2054,7 @@
         <v>-0.345957</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.14409</v>
+        <v>-0.283412</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>12.990606</v>
@@ -2170,7 +2170,7 @@
         <v>-0.340711</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.142372</v>
+        <v>-0.281694</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>12.990606</v>
@@ -2296,7 +2296,7 @@
         <v>-18.77725410102451</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-10.75874722404267</v>
+        <v>-8.333705572182225</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -2320,7 +2320,7 @@
         <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-0</v>
+        <v>-310.6535188086077</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>6.625289685822226</v>
@@ -6448,13 +6448,13 @@
         <v>-0.004673</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>0</v>
+        <v>-0.031653</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>0</v>
+        <v>0.030635</v>
       </c>
       <c r="M101" s="3" t="n">
-        <v>0</v>
+        <v>0.001238</v>
       </c>
       <c r="N101" s="3" t="n">
         <v>0</v>
@@ -6711,10 +6711,10 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0</v>
+        <v>0.10538</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.012394</v>
+        <v>-0.043512</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>-0.474645</v>
@@ -6738,13 +6738,13 @@
         <v>0.004567</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0.004387</v>
+        <v>-0.027266</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0.122127</v>
+        <v>0.152762</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>-0.043107</v>
+        <v>-0.041869</v>
       </c>
       <c r="N106" s="3" t="n">
         <v>2.141279</v>
@@ -7275,10 +7275,10 @@
         <v>0</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>0.05975</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>0</v>
+        <v>0.022315</v>
       </c>
       <c r="R115" s="3" t="n">
         <v>0</v>
@@ -23867,7 +23867,11 @@
           <t>Proceeds from disposal of marketable securities</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>-</t>
@@ -28700,7 +28704,11 @@
           <t>Deferred tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -29102,7 +29110,11 @@
           <t>Decrease in GST receivable</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -29791,7 +29803,11 @@
           <t>Net cash generated from investing activities</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>
@@ -30272,7 +30288,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -30775,7 +30795,11 @@
           <t>Decrease (increase) in GST receivable</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
           <t>-</t>
@@ -41760,7 +41784,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D333" t="inlineStr"/>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E333" s="5" t="n">
         <v>-0.65</v>
       </c>
@@ -42063,7 +42091,11 @@
           <t>Changes in non-cash operating working capital (Note 15)</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr"/>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E336" s="5" t="n">
         <v>0.10538</v>
       </c>
@@ -42265,7 +42297,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D338" t="inlineStr"/>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E338" s="5" t="n">
         <v>3.418</v>
       </c>
@@ -45354,7 +45390,11 @@
           <t>Loss from continuing operations $</t>
         </is>
       </c>
-      <c r="D369" t="inlineStr"/>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E369" t="inlineStr">
         <is>
           <t>-</t>
@@ -46774,7 +46814,11 @@
           <t>Net loss from discontinued operations 4</t>
         </is>
       </c>
-      <c r="D383" t="inlineStr"/>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E383" t="inlineStr">
         <is>
           <t>-</t>
@@ -48192,7 +48236,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D397" t="inlineStr"/>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E397" t="inlineStr">
         <is>
           <t>-</t>
@@ -48291,7 +48339,11 @@
           <t>Net loss from discontinued operation 4</t>
         </is>
       </c>
-      <c r="D398" t="inlineStr"/>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E398" t="inlineStr">
         <is>
           <t>-</t>
@@ -48590,7 +48642,11 @@
           <t>Income tax recovery</t>
         </is>
       </c>
-      <c r="D401" t="inlineStr"/>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E401" t="inlineStr">
         <is>
           <t>-</t>
@@ -54687,7 +54743,11 @@
           <t>Future income tax recovery (Note 14)</t>
         </is>
       </c>
-      <c r="D462" t="inlineStr"/>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E462" s="5" t="n">
         <v>0.65</v>
       </c>
